--- a/src/tools/source-excel/datasets.xlsx
+++ b/src/tools/source-excel/datasets.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daniaobert/Nextcloud/DANIA-OBERT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/caiazzo/HEDERA/CODES/WEBSITES/climate-risk-resouce-hub/src/tools/source-excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD01525B-F922-C54E-B59D-964AE63B87FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E91E2A-9012-8F4C-9D3F-7E0C0111053A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="980" yWindow="1160" windowWidth="27840" windowHeight="16660" xr2:uid="{B0CD518A-0E72-B848-BCBD-F99306A2A131}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="60">
   <si>
     <t>Format</t>
   </si>
@@ -315,6 +315,12 @@
   </si>
   <si>
     <t>Open Access</t>
+  </si>
+  <si>
+    <t>https://www.chc.ucsb.edu/data</t>
+  </si>
+  <si>
+    <t>CHIRPS</t>
   </si>
 </sst>
 </file>
@@ -404,8 +410,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Link" xfId="1" builtinId="8"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -421,7 +427,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -737,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2158586-FE74-8C48-B5A4-A1D4418A2B1B}">
-  <dimension ref="B3:K12"/>
+  <dimension ref="B3:K13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5" customWidth="1"/>
@@ -992,6 +998,14 @@
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
+    <row r="13" spans="2:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="B13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J13" t="s">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="J4" r:id="rId1" display="https://www.wri.org/data/aqueduct-water-risk-atlas" xr:uid="{896FE0DC-8A7D-5D42-B34F-653CB109DA92}"/>
